--- a/data/final/07_commits_gsynth.xlsx
+++ b/data/final/07_commits_gsynth.xlsx
@@ -394,19 +394,19 @@
         </is>
       </c>
       <c r="B2">
-        <v>0.186654531524323</v>
+        <v>0.1866545315243233</v>
       </c>
       <c r="C2">
-        <v>0.2928319380676137</v>
+        <v>0.2869006134036876</v>
       </c>
       <c r="D2">
-        <v>0.1774401685041867</v>
+        <v>0.175271447519597</v>
       </c>
       <c r="E2">
-        <v>-0.1611218081546012</v>
+        <v>-0.1568711931322888</v>
       </c>
       <c r="F2">
-        <v>0.5344308712032472</v>
+        <v>0.5301802561809354</v>
       </c>
     </row>
     <row r="3">
@@ -416,19 +416,19 @@
         </is>
       </c>
       <c r="B3">
-        <v>0.1256930501740114</v>
+        <v>0.1256930501740118</v>
       </c>
       <c r="C3">
-        <v>0.4444609535974298</v>
+        <v>0.4535740560421133</v>
       </c>
       <c r="D3">
-        <v>0.1643729778657623</v>
+        <v>0.1677092786199101</v>
       </c>
       <c r="E3">
-        <v>-0.1964720664744821</v>
+        <v>-0.2030110957942051</v>
       </c>
       <c r="F3">
-        <v>0.4478581668225049</v>
+        <v>0.4543971961422288</v>
       </c>
     </row>
     <row r="4">
@@ -438,19 +438,19 @@
         </is>
       </c>
       <c r="B4">
-        <v>-0.2401268083102857</v>
+        <v>-0.2401268083102852</v>
       </c>
       <c r="C4">
-        <v>0.03687014077937567</v>
+        <v>0.03083573584346588</v>
       </c>
       <c r="D4">
-        <v>0.1150473897139674</v>
+        <v>0.111211726411791</v>
       </c>
       <c r="E4">
-        <v>-0.4656155486650056</v>
+        <v>-0.4580977867359174</v>
       </c>
       <c r="F4">
-        <v>-0.01463806795556577</v>
+        <v>-0.02215582988465292</v>
       </c>
     </row>
     <row r="5">
@@ -460,19 +460,19 @@
         </is>
       </c>
       <c r="B5">
-        <v>-0.05347403947599123</v>
+        <v>-0.05347403947599081</v>
       </c>
       <c r="C5">
-        <v>0.6694148386458052</v>
+        <v>0.6875707717468482</v>
       </c>
       <c r="D5">
-        <v>0.1252462429213199</v>
+        <v>0.132969095451112</v>
       </c>
       <c r="E5">
-        <v>-0.2989521648007329</v>
+        <v>-0.3140886776170391</v>
       </c>
       <c r="F5">
-        <v>0.1920040858487504</v>
+        <v>0.2071405986650574</v>
       </c>
     </row>
     <row r="6">
@@ -482,19 +482,19 @@
         </is>
       </c>
       <c r="B6">
-        <v>0.1362460512208061</v>
+        <v>0.1362460512208064</v>
       </c>
       <c r="C6">
-        <v>0.2695043327274789</v>
+        <v>0.2707913615313648</v>
       </c>
       <c r="D6">
-        <v>0.1233883952232778</v>
+        <v>0.123720358862692</v>
       </c>
       <c r="E6">
-        <v>-0.1055907595270124</v>
+        <v>-0.1062413963044407</v>
       </c>
       <c r="F6">
-        <v>0.3780828619686246</v>
+        <v>0.3787334987460534</v>
       </c>
     </row>
     <row r="7">
@@ -507,16 +507,16 @@
         <v>0.1300363631481188</v>
       </c>
       <c r="C7">
-        <v>0.3025997298369727</v>
+        <v>0.3190705426345268</v>
       </c>
       <c r="D7">
-        <v>0.1261418122241441</v>
+        <v>0.1305101523228919</v>
       </c>
       <c r="E7">
-        <v>-0.1171970457558178</v>
+        <v>-0.1257588350215857</v>
       </c>
       <c r="F7">
-        <v>0.3772697720520554</v>
+        <v>0.3858315613178234</v>
       </c>
     </row>
     <row r="8">
@@ -526,19 +526,19 @@
         </is>
       </c>
       <c r="B8">
-        <v>0.07499873712850043</v>
+        <v>0.07499873712850058</v>
       </c>
       <c r="C8">
-        <v>0.5650817411817148</v>
+        <v>0.5788633814557143</v>
       </c>
       <c r="D8">
-        <v>0.1303623313604922</v>
+        <v>0.1351217260519189</v>
       </c>
       <c r="E8">
-        <v>-0.1805067372787407</v>
+        <v>-0.1898349794621479</v>
       </c>
       <c r="F8">
-        <v>0.3305042115357415</v>
+        <v>0.3398324537191491</v>
       </c>
     </row>
     <row r="9">
@@ -548,19 +548,19 @@
         </is>
       </c>
       <c r="B9">
-        <v>-0.1018229929218227</v>
+        <v>-0.1018229929218224</v>
       </c>
       <c r="C9">
-        <v>0.4373819628645734</v>
+        <v>0.4205311454465694</v>
       </c>
       <c r="D9">
-        <v>0.1311101476931024</v>
+        <v>0.1264096580658768</v>
       </c>
       <c r="E9">
-        <v>-0.3587941604080306</v>
+        <v>-0.3495813700289641</v>
       </c>
       <c r="F9">
-        <v>0.1551481745643851</v>
+        <v>0.1459353841853193</v>
       </c>
     </row>
     <row r="10">
@@ -573,16 +573,16 @@
         <v>-0.2583883908729895</v>
       </c>
       <c r="C10">
-        <v>0.08084435871727358</v>
+        <v>0.08402669491250192</v>
       </c>
       <c r="D10">
-        <v>0.1480050632793526</v>
+        <v>0.1495488859442645</v>
       </c>
       <c r="E10">
-        <v>-0.5484729844300922</v>
+        <v>-0.551498821251836</v>
       </c>
       <c r="F10">
-        <v>0.03169620268411316</v>
+        <v>0.03472203950585706</v>
       </c>
     </row>
     <row r="11">
@@ -595,16 +595,16 @@
         <v>-0.29659960214069</v>
       </c>
       <c r="C11">
-        <v>0.02842331859367442</v>
+        <v>0.02717705752699984</v>
       </c>
       <c r="D11">
-        <v>0.1353474775371227</v>
+        <v>0.1342708316195747</v>
       </c>
       <c r="E11">
-        <v>-0.5618757835117943</v>
+        <v>-0.5597655962892982</v>
       </c>
       <c r="F11">
-        <v>-0.03132342076958572</v>
+        <v>-0.03343360799208184</v>
       </c>
     </row>
     <row r="12">
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="B12">
-        <v>-0.06986613591016626</v>
+        <v>-0.06986613591016601</v>
       </c>
       <c r="C12">
-        <v>0.694463798167807</v>
+        <v>0.6952452617611209</v>
       </c>
       <c r="D12">
-        <v>0.1778648564882087</v>
+        <v>0.1783451071800382</v>
       </c>
       <c r="E12">
-        <v>-0.4184748487424405</v>
+        <v>-0.4194161228019764</v>
       </c>
       <c r="F12">
-        <v>0.2787425769221079</v>
+        <v>0.2796838509816444</v>
       </c>
     </row>
     <row r="13">
@@ -636,19 +636,19 @@
         </is>
       </c>
       <c r="B13">
-        <v>0.09663268440935682</v>
+        <v>0.09663268440935678</v>
       </c>
       <c r="C13">
-        <v>0.3832477217776553</v>
+        <v>0.3888048638688892</v>
       </c>
       <c r="D13">
-        <v>0.1108264644177365</v>
+        <v>0.1121306188820399</v>
       </c>
       <c r="E13">
-        <v>-0.1205831943833165</v>
+        <v>-0.1231392901636283</v>
       </c>
       <c r="F13">
-        <v>0.3138485632020301</v>
+        <v>0.3164046589823418</v>
       </c>
     </row>
     <row r="14">
@@ -658,19 +658,19 @@
         </is>
       </c>
       <c r="B14">
-        <v>0.4247403256752054</v>
+        <v>0.4247403256752053</v>
       </c>
       <c r="C14">
-        <v>0.002453623352728362</v>
+        <v>0.002376092653626483</v>
       </c>
       <c r="D14">
-        <v>0.140224470232148</v>
+        <v>0.1397774481364991</v>
       </c>
       <c r="E14">
-        <v>0.1499054142689865</v>
+        <v>0.1507815614767519</v>
       </c>
       <c r="F14">
-        <v>0.6995752370814243</v>
+        <v>0.6986990898736587</v>
       </c>
     </row>
     <row r="15">
@@ -680,19 +680,19 @@
         </is>
       </c>
       <c r="B15">
-        <v>-0.107410571267952</v>
+        <v>-0.1074105712679518</v>
       </c>
       <c r="C15">
-        <v>0.5197848803418015</v>
+        <v>0.5168997932837391</v>
       </c>
       <c r="D15">
-        <v>0.1668702847816506</v>
+        <v>0.1657233809011856</v>
       </c>
       <c r="E15">
-        <v>-0.4344703195299293</v>
+        <v>-0.4322224292304885</v>
       </c>
       <c r="F15">
-        <v>0.2196491769940253</v>
+        <v>0.2174012866945848</v>
       </c>
     </row>
     <row r="16">
@@ -702,19 +702,19 @@
         </is>
       </c>
       <c r="B16">
-        <v>0.1394611804620181</v>
+        <v>0.1394611804620183</v>
       </c>
       <c r="C16">
-        <v>0.409704598911159</v>
+        <v>0.3966281586537121</v>
       </c>
       <c r="D16">
-        <v>0.1691640981445763</v>
+        <v>0.1645251864949036</v>
       </c>
       <c r="E16">
-        <v>-0.1920943593785503</v>
+        <v>-0.1830022596177283</v>
       </c>
       <c r="F16">
-        <v>0.4710167203025866</v>
+        <v>0.4619246205417649</v>
       </c>
     </row>
     <row r="17">
@@ -724,19 +724,19 @@
         </is>
       </c>
       <c r="B17">
-        <v>0.002962273065507961</v>
+        <v>0.002962273065508369</v>
       </c>
       <c r="C17">
-        <v>0.9825845958643253</v>
+        <v>0.9822268952529238</v>
       </c>
       <c r="D17">
-        <v>0.1357053925614069</v>
+        <v>0.1329737543654715</v>
       </c>
       <c r="E17">
-        <v>-0.2630154088627192</v>
+        <v>-0.2576614963798916</v>
       </c>
       <c r="F17">
-        <v>0.2689399549937351</v>
+        <v>0.2635860425109083</v>
       </c>
     </row>
     <row r="18">
@@ -746,19 +746,19 @@
         </is>
       </c>
       <c r="B18">
-        <v>-0.02329142663498675</v>
+        <v>-0.02329142663498644</v>
       </c>
       <c r="C18">
-        <v>0.8570083798903771</v>
+        <v>0.863308097058219</v>
       </c>
       <c r="D18">
-        <v>0.1292649158225063</v>
+        <v>0.1352857754409492</v>
       </c>
       <c r="E18">
-        <v>-0.2766460061117008</v>
+        <v>-0.2884466741198202</v>
       </c>
       <c r="F18">
-        <v>0.2300631528417273</v>
+        <v>0.2418638208498473</v>
       </c>
     </row>
     <row r="19">
@@ -768,19 +768,19 @@
         </is>
       </c>
       <c r="B19">
-        <v>0.04882299641113464</v>
+        <v>0.04882299641113502</v>
       </c>
       <c r="C19">
-        <v>0.6654687394519767</v>
+        <v>0.6749299441614056</v>
       </c>
       <c r="D19">
-        <v>0.1129181238068862</v>
+        <v>0.1164138565402868</v>
       </c>
       <c r="E19">
-        <v>-0.1724924594521972</v>
+        <v>-0.1793439697092396</v>
       </c>
       <c r="F19">
-        <v>0.2701384522744665</v>
+        <v>0.2769899625315096</v>
       </c>
     </row>
     <row r="20">
@@ -790,19 +790,19 @@
         </is>
       </c>
       <c r="B20">
-        <v>0.05427492842671335</v>
+        <v>0.05427492842671387</v>
       </c>
       <c r="C20">
-        <v>0.6241532927109685</v>
+        <v>0.6426430773974743</v>
       </c>
       <c r="D20">
-        <v>0.1107713557502948</v>
+        <v>0.1169701859454945</v>
       </c>
       <c r="E20">
-        <v>-0.1628329393625382</v>
+        <v>-0.1749824232914086</v>
       </c>
       <c r="F20">
-        <v>0.2713827962159648</v>
+        <v>0.2835322801448363</v>
       </c>
     </row>
     <row r="21">
@@ -812,19 +812,19 @@
         </is>
       </c>
       <c r="B21">
-        <v>0.01460034324390101</v>
+        <v>0.01460034324390106</v>
       </c>
       <c r="C21">
-        <v>0.9230866289315856</v>
+        <v>0.9289520071557198</v>
       </c>
       <c r="D21">
-        <v>0.1512261892269584</v>
+        <v>0.1637480624628194</v>
       </c>
       <c r="E21">
-        <v>-0.2817975411601765</v>
+        <v>-0.3063399617214399</v>
       </c>
       <c r="F21">
-        <v>0.3109982276479786</v>
+        <v>0.3355406482092421</v>
       </c>
     </row>
     <row r="22">
@@ -834,19 +834,19 @@
         </is>
       </c>
       <c r="B22">
-        <v>-0.1212267388445747</v>
+        <v>-0.1212267388445736</v>
       </c>
       <c r="C22">
-        <v>0.3848074586800601</v>
+        <v>0.4049296271666769</v>
       </c>
       <c r="D22">
-        <v>0.1394897826635044</v>
+        <v>0.1455566009635743</v>
       </c>
       <c r="E22">
-        <v>-0.3946216890763627</v>
+        <v>-0.4065124344452473</v>
       </c>
       <c r="F22">
-        <v>0.1521682113872135</v>
+        <v>0.1640589567561</v>
       </c>
     </row>
     <row r="23">
@@ -856,19 +856,19 @@
         </is>
       </c>
       <c r="B23">
-        <v>-0.1910362732526778</v>
+        <v>-0.1910362732526771</v>
       </c>
       <c r="C23">
-        <v>0.2251046033736257</v>
+        <v>0.2400917760549108</v>
       </c>
       <c r="D23">
-        <v>0.1574821812191533</v>
+        <v>0.1626176336432665</v>
       </c>
       <c r="E23">
-        <v>-0.4996956766490283</v>
+        <v>-0.5097609784446084</v>
       </c>
       <c r="F23">
-        <v>0.1176231301436727</v>
+        <v>0.1276884319392542</v>
       </c>
     </row>
     <row r="24">
@@ -878,19 +878,19 @@
         </is>
       </c>
       <c r="B24">
-        <v>0.07039955294827377</v>
+        <v>0.07039955294827473</v>
       </c>
       <c r="C24">
-        <v>0.6068417800457684</v>
+        <v>0.6055004841766787</v>
       </c>
       <c r="D24">
-        <v>0.1368079219832314</v>
+        <v>0.1362993703982126</v>
       </c>
       <c r="E24">
-        <v>-0.1977390469386252</v>
+        <v>-0.1967423041477067</v>
       </c>
       <c r="F24">
-        <v>0.3385381528351727</v>
+        <v>0.3375414100442561</v>
       </c>
     </row>
     <row r="25">
@@ -900,19 +900,19 @@
         </is>
       </c>
       <c r="B25">
-        <v>-0.003850199545825576</v>
+        <v>-0.003850199545824948</v>
       </c>
       <c r="C25">
-        <v>0.981696089159271</v>
+        <v>0.9826304135104313</v>
       </c>
       <c r="D25">
-        <v>0.1678190701105838</v>
+        <v>0.1768477395613801</v>
       </c>
       <c r="E25">
-        <v>-0.3327695328815719</v>
+        <v>-0.3504653998334492</v>
       </c>
       <c r="F25">
-        <v>0.3250691337899208</v>
+        <v>0.3427650007417993</v>
       </c>
     </row>
     <row r="26">
@@ -922,19 +922,19 @@
         </is>
       </c>
       <c r="B26">
-        <v>0.08439653340000922</v>
+        <v>0.08439653340001063</v>
       </c>
       <c r="C26">
-        <v>0.5145139628955786</v>
+        <v>0.5071387355499661</v>
       </c>
       <c r="D26">
-        <v>0.1294772546130176</v>
+        <v>0.1272374382747991</v>
       </c>
       <c r="E26">
-        <v>-0.1693742224586277</v>
+        <v>-0.1649842631037336</v>
       </c>
       <c r="F26">
-        <v>0.3381672892586461</v>
+        <v>0.3337773299037549</v>
       </c>
     </row>
     <row r="27">
@@ -944,19 +944,19 @@
         </is>
       </c>
       <c r="B27">
-        <v>0.2524273687247454</v>
+        <v>0.2524273687247469</v>
       </c>
       <c r="C27">
-        <v>0.09982484997161301</v>
+        <v>0.09749308046604299</v>
       </c>
       <c r="D27">
-        <v>0.1533857055440086</v>
+        <v>0.1523279901966054</v>
       </c>
       <c r="E27">
-        <v>-0.04820308988477701</v>
+        <v>-0.04613000589797006</v>
       </c>
       <c r="F27">
-        <v>0.5530578273342679</v>
+        <v>0.5509847433474637</v>
       </c>
     </row>
     <row r="28">
@@ -966,19 +966,19 @@
         </is>
       </c>
       <c r="B28">
-        <v>0.01661802587219257</v>
+        <v>0.01661802587219378</v>
       </c>
       <c r="C28">
-        <v>0.9137925886191538</v>
+        <v>0.9157295852631466</v>
       </c>
       <c r="D28">
-        <v>0.1535066782371351</v>
+        <v>0.1570487636967049</v>
       </c>
       <c r="E28">
-        <v>-0.2842495348589706</v>
+        <v>-0.2911918947898893</v>
       </c>
       <c r="F28">
-        <v>0.3174855866033558</v>
+        <v>0.3244279465342769</v>
       </c>
     </row>
     <row r="29">
@@ -988,19 +988,19 @@
         </is>
       </c>
       <c r="B29">
-        <v>0.127903385766672</v>
+        <v>0.1279033857666734</v>
       </c>
       <c r="C29">
-        <v>0.3471804010312167</v>
+        <v>0.3206073143103394</v>
       </c>
       <c r="D29">
-        <v>0.1360569456520097</v>
+        <v>0.1287777039793738</v>
       </c>
       <c r="E29">
-        <v>-0.1387633275577903</v>
+        <v>-0.1244962760446595</v>
       </c>
       <c r="F29">
-        <v>0.3945700990911344</v>
+        <v>0.3803030475780063</v>
       </c>
     </row>
     <row r="30">
@@ -1010,19 +1010,19 @@
         </is>
       </c>
       <c r="B30">
-        <v>-0.1616312808040966</v>
+        <v>-0.1616312808040956</v>
       </c>
       <c r="C30">
-        <v>0.1991291997078302</v>
+        <v>0.1918295728891688</v>
       </c>
       <c r="D30">
-        <v>0.1258774857799072</v>
+        <v>0.1238377518451396</v>
       </c>
       <c r="E30">
-        <v>-0.4083466193971674</v>
+        <v>-0.4043488143469777</v>
       </c>
       <c r="F30">
-        <v>0.08508405778897424</v>
+        <v>0.08108625273878645</v>
       </c>
     </row>
     <row r="31">
@@ -1032,19 +1032,19 @@
         </is>
       </c>
       <c r="B31">
-        <v>-0.06986260325690517</v>
+        <v>-0.06986260325690398</v>
       </c>
       <c r="C31">
-        <v>0.6146333860206306</v>
+        <v>0.6084665289524336</v>
       </c>
       <c r="D31">
-        <v>0.1387620081379223</v>
+        <v>0.1363801795237522</v>
       </c>
       <c r="E31">
-        <v>-0.3418311416296867</v>
+        <v>-0.3371628433285651</v>
       </c>
       <c r="F31">
-        <v>0.2021059351158763</v>
+        <v>0.1974376368147571</v>
       </c>
     </row>
     <row r="32">
@@ -1054,19 +1054,19 @@
         </is>
       </c>
       <c r="B32">
-        <v>-0.04499835899808586</v>
+        <v>-0.04499835899808481</v>
       </c>
       <c r="C32">
-        <v>0.7790814856866135</v>
+        <v>0.7808318864802448</v>
       </c>
       <c r="D32">
-        <v>0.160412683266663</v>
+        <v>0.1617278257570914</v>
       </c>
       <c r="E32">
-        <v>-0.3594014408641762</v>
+        <v>-0.3619790727799531</v>
       </c>
       <c r="F32">
-        <v>0.2694047228680045</v>
+        <v>0.2719823547837835</v>
       </c>
     </row>
     <row r="33">
@@ -1076,19 +1076,19 @@
         </is>
       </c>
       <c r="B33">
-        <v>-0.17375492183083</v>
+        <v>-0.1737549218308289</v>
       </c>
       <c r="C33">
-        <v>0.3205116591898256</v>
+        <v>0.3040354927574274</v>
       </c>
       <c r="D33">
-        <v>0.1749080935960299</v>
+        <v>0.1690522427962459</v>
       </c>
       <c r="E33">
-        <v>-0.5165684858836094</v>
+        <v>-0.5050912292171916</v>
       </c>
       <c r="F33">
-        <v>0.1690586422219493</v>
+        <v>0.1575813855555337</v>
       </c>
     </row>
     <row r="34">
@@ -1098,19 +1098,19 @@
         </is>
       </c>
       <c r="B34">
-        <v>-0.0493471439734729</v>
+        <v>-0.04934714397347278</v>
       </c>
       <c r="C34">
-        <v>0.7078736579071405</v>
+        <v>0.712209254364033</v>
       </c>
       <c r="D34">
-        <v>0.1316930478626119</v>
+        <v>0.1337717500705123</v>
       </c>
       <c r="E34">
-        <v>-0.3074607747985017</v>
+        <v>-0.3115349562605702</v>
       </c>
       <c r="F34">
-        <v>0.2087664868515559</v>
+        <v>0.2128406683136246</v>
       </c>
     </row>
     <row r="35">
@@ -1120,19 +1120,19 @@
         </is>
       </c>
       <c r="B35">
-        <v>0.07177022267434717</v>
+        <v>0.07177022267434681</v>
       </c>
       <c r="C35">
-        <v>0.5386797882940366</v>
+        <v>0.5696993523532652</v>
       </c>
       <c r="D35">
-        <v>0.1167354940835445</v>
+        <v>0.1262461531408647</v>
       </c>
       <c r="E35">
-        <v>-0.1570271414468886</v>
+        <v>-0.1756676906684762</v>
       </c>
       <c r="F35">
-        <v>0.3005675867955829</v>
+        <v>0.3192081360171698</v>
       </c>
     </row>
     <row r="36">
@@ -1142,19 +1142,19 @@
         </is>
       </c>
       <c r="B36">
-        <v>-0.06060054952277381</v>
+        <v>-0.06060054952277451</v>
       </c>
       <c r="C36">
-        <v>0.5946664267640964</v>
+        <v>0.6048522640970124</v>
       </c>
       <c r="D36">
-        <v>0.113892394174082</v>
+        <v>0.1171171344798875</v>
       </c>
       <c r="E36">
-        <v>-0.283825540217014</v>
+        <v>-0.2901459150758881</v>
       </c>
       <c r="F36">
-        <v>0.1626244411714664</v>
+        <v>0.1689448160303391</v>
       </c>
     </row>
     <row r="37">
@@ -1164,19 +1164,19 @@
         </is>
       </c>
       <c r="B37">
-        <v>0.06291510588101205</v>
+        <v>0.06291510588101115</v>
       </c>
       <c r="C37">
-        <v>0.6460468862460393</v>
+        <v>0.639031825538833</v>
       </c>
       <c r="D37">
-        <v>0.1369921064176001</v>
+        <v>0.1341322185910179</v>
       </c>
       <c r="E37">
-        <v>-0.2055844888637625</v>
+        <v>-0.1999792117238378</v>
       </c>
       <c r="F37">
-        <v>0.3314147006257867</v>
+        <v>0.3258094234858601</v>
       </c>
     </row>
     <row r="38">
@@ -1186,19 +1186,19 @@
         </is>
       </c>
       <c r="B38">
-        <v>-0.02729096938656783</v>
+        <v>-0.02729096938656848</v>
       </c>
       <c r="C38">
-        <v>0.8205713820079086</v>
+        <v>0.8235954113937463</v>
       </c>
       <c r="D38">
-        <v>0.1203251755641398</v>
+        <v>0.1224232834505046</v>
       </c>
       <c r="E38">
-        <v>-0.2631239799257407</v>
+        <v>-0.2672361958186958</v>
       </c>
       <c r="F38">
-        <v>0.208542041152605</v>
+        <v>0.2126542570455588</v>
       </c>
     </row>
     <row r="39">
@@ -1208,19 +1208,19 @@
         </is>
       </c>
       <c r="B39">
-        <v>0.07558126010977714</v>
+        <v>0.07558126010977599</v>
       </c>
       <c r="C39">
-        <v>0.5407923121784675</v>
+        <v>0.5001440855447257</v>
       </c>
       <c r="D39">
-        <v>0.1235764703392818</v>
+        <v>0.1120946181778151</v>
       </c>
       <c r="E39">
-        <v>-0.1666241710917973</v>
+        <v>-0.1441201543795105</v>
       </c>
       <c r="F39">
-        <v>0.3177866913113516</v>
+        <v>0.2952826745990624</v>
       </c>
     </row>
     <row r="40">
@@ -1230,19 +1230,19 @@
         </is>
       </c>
       <c r="B40">
-        <v>-0.09431770793524777</v>
+        <v>-0.09431770793524863</v>
       </c>
       <c r="C40">
-        <v>0.5663309029092771</v>
+        <v>0.535757828742476</v>
       </c>
       <c r="D40">
-        <v>0.1644702883406474</v>
+        <v>0.1523118777715146</v>
       </c>
       <c r="E40">
-        <v>-0.4166735496098345</v>
+        <v>-0.3928435027850839</v>
       </c>
       <c r="F40">
-        <v>0.2280381337393389</v>
+        <v>0.2042080869145866</v>
       </c>
     </row>
     <row r="41">
@@ -1252,19 +1252,19 @@
         </is>
       </c>
       <c r="B41">
-        <v>0.1509200218751393</v>
+        <v>0.1509200218751385</v>
       </c>
       <c r="C41">
-        <v>0.2256071962725044</v>
+        <v>0.2061783455138675</v>
       </c>
       <c r="D41">
-        <v>0.1245469198691564</v>
+        <v>0.1193851504294557</v>
       </c>
       <c r="E41">
-        <v>-0.09318745545380328</v>
+        <v>-0.08307057325549125</v>
       </c>
       <c r="F41">
-        <v>0.3950274992040818</v>
+        <v>0.3849106170057682</v>
       </c>
     </row>
     <row r="42">
@@ -1274,19 +1274,19 @@
         </is>
       </c>
       <c r="B42">
-        <v>-0.1900322272188448</v>
+        <v>-0.1900322272188458</v>
       </c>
       <c r="C42">
-        <v>0.1920049771625374</v>
+        <v>0.2162292176638898</v>
       </c>
       <c r="D42">
-        <v>0.1456553108314906</v>
+        <v>0.1536710160379047</v>
       </c>
       <c r="E42">
-        <v>-0.4755113906055532</v>
+        <v>-0.4912218841208159</v>
       </c>
       <c r="F42">
-        <v>0.09544693616786354</v>
+        <v>0.1111574296831243</v>
       </c>
     </row>
     <row r="43">
@@ -1296,19 +1296,19 @@
         </is>
       </c>
       <c r="B43">
-        <v>0.01896250231096303</v>
+        <v>0.0189625023109623</v>
       </c>
       <c r="C43">
-        <v>0.8953894905698014</v>
+        <v>0.9009273947201168</v>
       </c>
       <c r="D43">
-        <v>0.1442149924357102</v>
+        <v>0.1523216093012868</v>
       </c>
       <c r="E43">
-        <v>-0.2636936888937453</v>
+        <v>-0.279582365986741</v>
       </c>
       <c r="F43">
-        <v>0.3016186935156713</v>
+        <v>0.3175073706086656</v>
       </c>
     </row>
     <row r="44">
@@ -1318,19 +1318,19 @@
         </is>
       </c>
       <c r="B44">
-        <v>0.2072854218537008</v>
+        <v>0.2072854218537004</v>
       </c>
       <c r="C44">
-        <v>0.07016543469683878</v>
+        <v>0.07620930975189144</v>
       </c>
       <c r="D44">
-        <v>0.1144691320132774</v>
+        <v>0.1169045322469349</v>
       </c>
       <c r="E44">
-        <v>-0.01706995423388386</v>
+        <v>-0.0218432509797932</v>
       </c>
       <c r="F44">
-        <v>0.4316407979412854</v>
+        <v>0.4364140946871941</v>
       </c>
     </row>
     <row r="45">
@@ -1340,19 +1340,19 @@
         </is>
       </c>
       <c r="B45">
-        <v>-0.1270625740569555</v>
+        <v>-0.1270625740569558</v>
       </c>
       <c r="C45">
-        <v>0.3889604993379576</v>
+        <v>0.4186676282154391</v>
       </c>
       <c r="D45">
-        <v>0.1474892383221066</v>
+        <v>0.1571127552190024</v>
       </c>
       <c r="E45">
-        <v>-0.4161361692755292</v>
+        <v>-0.4349979157980577</v>
       </c>
       <c r="F45">
-        <v>0.1620110211616181</v>
+        <v>0.1808727676841462</v>
       </c>
     </row>
     <row r="46">
@@ -1362,19 +1362,19 @@
         </is>
       </c>
       <c r="B46">
-        <v>0.09546121066971149</v>
+        <v>0.09546121066971125</v>
       </c>
       <c r="C46">
-        <v>0.3463919139012144</v>
+        <v>0.4008729253772931</v>
       </c>
       <c r="D46">
-        <v>0.1013807465190168</v>
+        <v>0.1136357422548343</v>
       </c>
       <c r="E46">
-        <v>-0.1032414012333457</v>
+        <v>-0.1272607515062404</v>
       </c>
       <c r="F46">
-        <v>0.2941638225727687</v>
+        <v>0.3181831728456629</v>
       </c>
     </row>
     <row r="47">
@@ -1384,19 +1384,19 @@
         </is>
       </c>
       <c r="B47">
-        <v>-0.1354863202326591</v>
+        <v>-0.1354863202326593</v>
       </c>
       <c r="C47">
-        <v>0.3590473930222657</v>
+        <v>0.3396707173892866</v>
       </c>
       <c r="D47">
-        <v>0.147720248350171</v>
+        <v>0.1418978209158415</v>
       </c>
       <c r="E47">
-        <v>-0.4250126867863064</v>
+        <v>-0.4136009387124229</v>
       </c>
       <c r="F47">
-        <v>0.1540400463209883</v>
+        <v>0.1426282982471043</v>
       </c>
     </row>
     <row r="48">
@@ -1406,19 +1406,19 @@
         </is>
       </c>
       <c r="B48">
-        <v>0.0416839466943292</v>
+        <v>0.04168394669432944</v>
       </c>
       <c r="C48">
-        <v>0.6568706143074043</v>
+        <v>0.6715668143723534</v>
       </c>
       <c r="D48">
-        <v>0.09383249241946247</v>
+        <v>0.09831151331161764</v>
       </c>
       <c r="E48">
-        <v>-0.1422243590274448</v>
+        <v>-0.1510030786620712</v>
       </c>
       <c r="F48">
-        <v>0.2255922524161032</v>
+        <v>0.23437097205073</v>
       </c>
     </row>
     <row r="49">
@@ -1428,19 +1428,19 @@
         </is>
       </c>
       <c r="B49">
-        <v>-0.06042273942211485</v>
+        <v>-0.06042273942211442</v>
       </c>
       <c r="C49">
-        <v>0.6905219674180754</v>
+        <v>0.6938393170137642</v>
       </c>
       <c r="D49">
-        <v>0.151759946695382</v>
+        <v>0.1534934828032371</v>
       </c>
       <c r="E49">
-        <v>-0.3578667692407818</v>
+        <v>-0.3612644375780772</v>
       </c>
       <c r="F49">
-        <v>0.2370212903965521</v>
+        <v>0.2404189587338484</v>
       </c>
     </row>
     <row r="50">
@@ -1450,19 +1450,19 @@
         </is>
       </c>
       <c r="B50">
-        <v>-0.2635824067688365</v>
+        <v>-0.263582406768836</v>
       </c>
       <c r="C50">
-        <v>0.05247931267161343</v>
+        <v>0.06064369159354399</v>
       </c>
       <c r="D50">
-        <v>0.1359246085415468</v>
+        <v>0.1404960282810343</v>
       </c>
       <c r="E50">
-        <v>-0.5299897441229736</v>
+        <v>-0.538949562170584</v>
       </c>
       <c r="F50">
-        <v>0.002824930585300534</v>
+        <v>0.01178474863291196</v>
       </c>
     </row>
     <row r="51">
@@ -1472,19 +1472,19 @@
         </is>
       </c>
       <c r="B51">
-        <v>0.04111898224276807</v>
+        <v>0.04111898224276889</v>
       </c>
       <c r="C51">
-        <v>0.7133265257806858</v>
+        <v>0.7344341149189491</v>
       </c>
       <c r="D51">
-        <v>0.1119212323317965</v>
+        <v>0.1212115765567642</v>
       </c>
       <c r="E51">
-        <v>-0.1782426022328929</v>
+        <v>-0.1964513423178084</v>
       </c>
       <c r="F51">
-        <v>0.260480566718429</v>
+        <v>0.2786893068033462</v>
       </c>
     </row>
     <row r="52">
@@ -1494,19 +1494,19 @@
         </is>
       </c>
       <c r="B52">
-        <v>0.07851303311052332</v>
+        <v>0.07851303311052407</v>
       </c>
       <c r="C52">
-        <v>0.4905294311384727</v>
+        <v>0.5195700068033584</v>
       </c>
       <c r="D52">
-        <v>0.1138749682747278</v>
+        <v>0.1219130633073752</v>
       </c>
       <c r="E52">
-        <v>-0.1446778034485843</v>
+        <v>-0.1604321802168827</v>
       </c>
       <c r="F52">
-        <v>0.3017038696696309</v>
+        <v>0.3174582464379309</v>
       </c>
     </row>
     <row r="53">
@@ -1516,19 +1516,19 @@
         </is>
       </c>
       <c r="B53">
-        <v>0.06334097137758282</v>
+        <v>0.06334097137758306</v>
       </c>
       <c r="C53">
-        <v>0.5596284524701192</v>
+        <v>0.5436800020556729</v>
       </c>
       <c r="D53">
-        <v>0.1085733293165399</v>
+        <v>0.1043066008823919</v>
       </c>
       <c r="E53">
-        <v>-0.149458843764442</v>
+        <v>-0.1410962097016988</v>
       </c>
       <c r="F53">
-        <v>0.2761407865196077</v>
+        <v>0.2677781524568649</v>
       </c>
     </row>
     <row r="54">
@@ -1538,19 +1538,19 @@
         </is>
       </c>
       <c r="B54">
-        <v>0.1383039982675726</v>
+        <v>0.1383039982675732</v>
       </c>
       <c r="C54">
-        <v>0.3219067635939696</v>
+        <v>0.3429721452746042</v>
       </c>
       <c r="D54">
-        <v>0.1396238439504871</v>
+        <v>0.1458427485668132</v>
       </c>
       <c r="E54">
-        <v>-0.1353537072584227</v>
+        <v>-0.1475425363297111</v>
       </c>
       <c r="F54">
-        <v>0.4119617037935679</v>
+        <v>0.4241505328648576</v>
       </c>
     </row>
     <row r="55">
@@ -1560,19 +1560,19 @@
         </is>
       </c>
       <c r="B55">
-        <v>0.3880562746092892</v>
+        <v>0.3880562746092898</v>
       </c>
       <c r="C55">
-        <v>0.02422812897272575</v>
+        <v>0.03733576806976635</v>
       </c>
       <c r="D55">
-        <v>0.1722021786316552</v>
+        <v>0.186379730541945</v>
       </c>
       <c r="E55">
-        <v>0.05054620643191227</v>
+        <v>0.02275871529879775</v>
       </c>
       <c r="F55">
-        <v>0.7255663427866661</v>
+        <v>0.7533538339197818</v>
       </c>
     </row>
     <row r="56">
@@ -1582,19 +1582,19 @@
         </is>
       </c>
       <c r="B56">
-        <v>0.3251984889156921</v>
+        <v>0.3251984889156931</v>
       </c>
       <c r="C56">
-        <v>0.08307704950475103</v>
+        <v>0.09261575749079531</v>
       </c>
       <c r="D56">
-        <v>0.1876392560831824</v>
+        <v>0.1933681721239104</v>
       </c>
       <c r="E56">
-        <v>-0.04256769509323349</v>
+        <v>-0.05379616420351324</v>
       </c>
       <c r="F56">
-        <v>0.6929646729246177</v>
+        <v>0.7041931420348995</v>
       </c>
     </row>
     <row r="57">
@@ -1604,19 +1604,19 @@
         </is>
       </c>
       <c r="B57">
-        <v>0.1405739465331424</v>
+        <v>0.140573946533143</v>
       </c>
       <c r="C57">
-        <v>0.4418861667510969</v>
+        <v>0.4668920968332106</v>
       </c>
       <c r="D57">
-        <v>0.1827981102451181</v>
+        <v>0.1932168138987253</v>
       </c>
       <c r="E57">
-        <v>-0.2177037659892712</v>
+        <v>-0.2381240499159366</v>
       </c>
       <c r="F57">
-        <v>0.498851659055556</v>
+        <v>0.5192719429822226</v>
       </c>
     </row>
     <row r="58">
@@ -1626,19 +1626,19 @@
         </is>
       </c>
       <c r="B58">
-        <v>0.4137294694287965</v>
+        <v>0.413729469428797</v>
       </c>
       <c r="C58">
-        <v>0.01902249675326817</v>
+        <v>0.0151571282905818</v>
       </c>
       <c r="D58">
-        <v>0.1764237203802445</v>
+        <v>0.1703569940324056</v>
       </c>
       <c r="E58">
-        <v>0.06794533146495219</v>
+        <v>0.07983589661077722</v>
       </c>
       <c r="F58">
-        <v>0.7595136073926407</v>
+        <v>0.7476230422468166</v>
       </c>
     </row>
     <row r="59">
@@ -1648,19 +1648,19 @@
         </is>
       </c>
       <c r="B59">
-        <v>0.3815787506229547</v>
+        <v>0.3815787506229558</v>
       </c>
       <c r="C59">
-        <v>0.1159284696216842</v>
+        <v>0.09403497681675232</v>
       </c>
       <c r="D59">
-        <v>0.242719871847723</v>
+        <v>0.2278780355929202</v>
       </c>
       <c r="E59">
-        <v>-0.09414345653075956</v>
+        <v>-0.06505399200690426</v>
       </c>
       <c r="F59">
-        <v>0.857300957776669</v>
+        <v>0.8282114932528157</v>
       </c>
     </row>
     <row r="60">
@@ -1670,19 +1670,19 @@
         </is>
       </c>
       <c r="B60">
-        <v>0.564996841996101</v>
+        <v>0.5649968419961019</v>
       </c>
       <c r="C60">
-        <v>0.01057946025785927</v>
+        <v>0.007187534073327395</v>
       </c>
       <c r="D60">
-        <v>0.2210221142219791</v>
+        <v>0.2101900776270479</v>
       </c>
       <c r="E60">
-        <v>0.1318014583341241</v>
+        <v>0.15303185993941</v>
       </c>
       <c r="F60">
-        <v>0.998192225658078</v>
+        <v>0.9769618240527937</v>
       </c>
     </row>
     <row r="61">
@@ -1692,19 +1692,19 @@
         </is>
       </c>
       <c r="B61">
-        <v>0.6649561972376428</v>
+        <v>0.6649561972376438</v>
       </c>
       <c r="C61">
-        <v>0.009008700351409438</v>
+        <v>0.009257386486603236</v>
       </c>
       <c r="D61">
-        <v>0.2546043337844969</v>
+        <v>0.2555165426348792</v>
       </c>
       <c r="E61">
-        <v>0.1659408727122144</v>
+        <v>0.1641529762190874</v>
       </c>
       <c r="F61">
-        <v>1.163971521763071</v>
+        <v>1.1657594182562</v>
       </c>
     </row>
     <row r="62">
@@ -1714,19 +1714,19 @@
         </is>
       </c>
       <c r="B62">
-        <v>0.5594161793494684</v>
+        <v>0.5594161793494697</v>
       </c>
       <c r="C62">
-        <v>0.006968042846009492</v>
+        <v>0.005702088314088583</v>
       </c>
       <c r="D62">
-        <v>0.2073165118638007</v>
+        <v>0.2023616051358545</v>
       </c>
       <c r="E62">
-        <v>0.1530832826959484</v>
+        <v>0.1627947214294795</v>
       </c>
       <c r="F62">
-        <v>0.9657490760029884</v>
+        <v>0.95603763726946</v>
       </c>
     </row>
     <row r="63">
@@ -1736,19 +1736,19 @@
         </is>
       </c>
       <c r="B63">
-        <v>0.6395927402386867</v>
+        <v>0.6395927402386878</v>
       </c>
       <c r="C63">
-        <v>0.008323312791651327</v>
+        <v>0.005285733691498429</v>
       </c>
       <c r="D63">
-        <v>0.242392529487814</v>
+        <v>0.2293199906702354</v>
       </c>
       <c r="E63">
-        <v>0.1645121123210085</v>
+        <v>0.1901338175899654</v>
       </c>
       <c r="F63">
-        <v>1.114673368156365</v>
+        <v>1.08905166288741</v>
       </c>
     </row>
     <row r="64">
@@ -1758,19 +1758,19 @@
         </is>
       </c>
       <c r="B64">
-        <v>0.8272997631561713</v>
+        <v>0.8272997631561725</v>
       </c>
       <c r="C64">
-        <v>0.0005431884555764377</v>
+        <v>0.000420277278861958</v>
       </c>
       <c r="D64">
-        <v>0.2392075496134261</v>
+        <v>0.2345610671899985</v>
       </c>
       <c r="E64">
-        <v>0.3584615810837782</v>
+        <v>0.3675685192884959</v>
       </c>
       <c r="F64">
-        <v>1.296137945228564</v>
+        <v>1.287031007023849</v>
       </c>
     </row>
     <row r="65">
@@ -1780,19 +1780,19 @@
         </is>
       </c>
       <c r="B65">
-        <v>0.9930650681514511</v>
+        <v>0.9930650681514522</v>
       </c>
       <c r="C65">
-        <v>0.003530485686882079</v>
+        <v>0.003322773045206562</v>
       </c>
       <c r="D65">
-        <v>0.3404027079267294</v>
+        <v>0.3382162397896439</v>
       </c>
       <c r="E65">
-        <v>0.3258880203751546</v>
+        <v>0.3301734191771877</v>
       </c>
       <c r="F65">
-        <v>1.660242115927748</v>
+        <v>1.655956717125717</v>
       </c>
     </row>
     <row r="66">
@@ -1802,19 +1802,19 @@
         </is>
       </c>
       <c r="B66">
-        <v>1.633477546906216</v>
+        <v>1.633477546906217</v>
       </c>
       <c r="C66">
-        <v>0.002223057326432132</v>
+        <v>0.002961140260106632</v>
       </c>
       <c r="D66">
-        <v>0.5340445066644331</v>
+        <v>0.5496697765756819</v>
       </c>
       <c r="E66">
-        <v>0.5867695477024668</v>
+        <v>0.5561445814277024</v>
       </c>
       <c r="F66">
-        <v>2.680185546109966</v>
+        <v>2.710810512384731</v>
       </c>
     </row>
   </sheetData>
@@ -1866,19 +1866,19 @@
         </is>
       </c>
       <c r="B2">
-        <v>0.516523630555571</v>
+        <v>0.5165236305555718</v>
       </c>
       <c r="C2">
-        <v>0.003042897561492452</v>
+        <v>0.002543621431383425</v>
       </c>
       <c r="D2">
-        <v>0.1743027324493857</v>
+        <v>0.1711417970128456</v>
       </c>
       <c r="E2">
-        <v>0.1748965525478543</v>
+        <v>0.18109187216093</v>
       </c>
       <c r="F2">
-        <v>0.8581507085632878</v>
+        <v>0.8519553889502136</v>
       </c>
     </row>
   </sheetData>
